--- a/Deliverables/Phase_2/ASVS_5_0_Tracker_SecureMarket.xlsx
+++ b/Deliverables/Phase_2/ASVS_5_0_Tracker_SecureMarket.xlsx
@@ -2784,12 +2784,12 @@
       </c>
       <c r="F3" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G3" s="47" t="inlineStr">
         <is>
-          <t>SR-AUTH-06: JWT signature validated using HS256/RS256 before accepting token contents.</t>
+          <t>JWT signature verified with PyJWT before use (core/security.py decode_*).</t>
         </is>
       </c>
       <c r="H3" s="47" t="n"/>
@@ -2820,12 +2820,12 @@
       </c>
       <c r="F4" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G4" s="52" t="inlineStr">
         <is>
-          <t>SR-AUTH-06: Only HS256 or RS256 permitted; 'none' algorithm explicitly rejected.</t>
+          <t>decode_* pass an explicit algorithms allow-list ([HS256]); the 'none' algorithm is rejected.</t>
         </is>
       </c>
       <c r="H4" s="52" t="n"/>
@@ -2856,12 +2856,12 @@
       </c>
       <c r="F5" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G5" s="47" t="inlineStr">
         <is>
-          <t>SR-AUTH-06: Signing secret loaded from environment variables only; no dynamic key source headers accepted.</t>
+          <t>Symmetric HS256 key from environment only; no header-driven key resolution (jku/x5u/jwk not honored for HS256).</t>
         </is>
       </c>
       <c r="H5" s="47" t="n"/>
@@ -2910,12 +2910,12 @@
       </c>
       <c r="F7" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G7" s="47" t="inlineStr">
         <is>
-          <t>SR-AUTH-05: JWT exp and nbf claims validated on every request; expired tokens rejected.</t>
+          <t>exp is set and verified (PyJWT validates expiry by default); iat-based revocation cutoff also enforced.</t>
         </is>
       </c>
       <c r="H7" s="47" t="n"/>
@@ -2946,12 +2946,12 @@
       </c>
       <c r="F8" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G8" s="52" t="inlineStr">
         <is>
-          <t>Access tokens and refresh tokens are distinguished by type claim; each accepted only for its intended purpose.</t>
+          <t>Token 'type' claim is checked: access vs refresh enforced (decode_access_token/decode_refresh_token).</t>
         </is>
       </c>
       <c r="H8" s="52" t="n"/>
@@ -2982,12 +2982,12 @@
       </c>
       <c r="F9" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G9" s="47" t="inlineStr">
         <is>
-          <t>Single-service deployment; audience restriction not implemented but no cross-service token reuse risk.</t>
+          <t>Single-service monolith; no 'aud' claim / multi-audience scenario.</t>
         </is>
       </c>
       <c r="H9" s="47" t="n"/>
@@ -3018,12 +3018,12 @@
       </c>
       <c r="F10" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G10" s="52" t="inlineStr">
         <is>
-          <t>Single issuer and single audience; audience uniqueness requirement not applicable.</t>
+          <t>One signing key, single audience; no cross-audience reuse risk.</t>
         </is>
       </c>
       <c r="H10" s="52" t="n"/>
@@ -3157,12 +3157,12 @@
       </c>
       <c r="F3" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G3" s="47" t="inlineStr">
         <is>
-          <t>SecureMarket uses custom JWT authentication, not OAuth/OIDC.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H3" s="47" t="n"/>
@@ -3193,12 +3193,12 @@
       </c>
       <c r="F4" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G4" s="52" t="inlineStr">
         <is>
-          <t>No OAuth/OIDC authorization flow implemented.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H4" s="52" t="n"/>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="F6" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G6" s="47" t="inlineStr">
         <is>
-          <t>No OAuth client; custom authentication only.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H6" s="47" t="n"/>
@@ -3283,12 +3283,12 @@
       </c>
       <c r="F7" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G7" s="52" t="inlineStr">
         <is>
-          <t>No OAuth client; single authentication system.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H7" s="52" t="n"/>
@@ -3319,12 +3319,12 @@
       </c>
       <c r="F8" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G8" s="47" t="inlineStr">
         <is>
-          <t>No OAuth scopes; RBAC used instead.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H8" s="47" t="n"/>
@@ -3373,12 +3373,12 @@
       </c>
       <c r="F10" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G10" s="47" t="inlineStr">
         <is>
-          <t>No OAuth resource server; custom JWT validation.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H10" s="47" t="n"/>
@@ -3409,12 +3409,12 @@
       </c>
       <c r="F11" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G11" s="52" t="inlineStr">
         <is>
-          <t>No OAuth; authorization based on JWT claims (role, user_id).</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H11" s="52" t="n"/>
@@ -3445,12 +3445,12 @@
       </c>
       <c r="F12" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G12" s="47" t="inlineStr">
         <is>
-          <t>No OAuth; user identified from JWT sub claim.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H12" s="47" t="n"/>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="F13" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G13" s="52" t="inlineStr">
         <is>
-          <t>No OAuth; no acr/amr/auth_time claims.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H13" s="52" t="n"/>
@@ -3517,12 +3517,12 @@
       </c>
       <c r="F14" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G14" s="47" t="inlineStr">
         <is>
-          <t>No OAuth; sender-constrained tokens not applicable.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H14" s="47" t="n"/>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="F16" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G16" s="47" t="inlineStr">
         <is>
-          <t>No OAuth authorization server.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H16" s="47" t="n"/>
@@ -3607,12 +3607,12 @@
       </c>
       <c r="F17" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G17" s="52" t="inlineStr">
         <is>
-          <t>No authorization codes; direct JWT issuance.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H17" s="52" t="n"/>
@@ -3643,12 +3643,12 @@
       </c>
       <c r="F18" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G18" s="47" t="inlineStr">
         <is>
-          <t>No authorization codes.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H18" s="47" t="n"/>
@@ -3679,12 +3679,12 @@
       </c>
       <c r="F19" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G19" s="52" t="inlineStr">
         <is>
-          <t>No OAuth grant types.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H19" s="52" t="n"/>
@@ -3715,12 +3715,12 @@
       </c>
       <c r="F20" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G20" s="47" t="inlineStr">
         <is>
-          <t>No OAuth refresh tokens in OAuth sense; custom refresh token mechanism used.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H20" s="47" t="n"/>
@@ -3751,12 +3751,12 @@
       </c>
       <c r="F21" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G21" s="52" t="inlineStr">
         <is>
-          <t>No PKCE; not an OAuth implementation.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H21" s="52" t="n"/>
@@ -3787,12 +3787,12 @@
       </c>
       <c r="F22" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G22" s="47" t="inlineStr">
         <is>
-          <t>No dynamic client registration.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H22" s="47" t="n"/>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="F23" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G23" s="52" t="inlineStr">
         <is>
-          <t>No OAuth refresh tokens.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H23" s="52" t="n"/>
@@ -3859,12 +3859,12 @@
       </c>
       <c r="F24" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G24" s="47" t="inlineStr">
         <is>
-          <t>No OAuth authorization server.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H24" s="47" t="n"/>
@@ -3895,12 +3895,12 @@
       </c>
       <c r="F25" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G25" s="52" t="inlineStr">
         <is>
-          <t>No OAuth confidential clients.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H25" s="52" t="n"/>
@@ -3931,12 +3931,12 @@
       </c>
       <c r="F26" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G26" s="47" t="inlineStr">
         <is>
-          <t>No OAuth scopes.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H26" s="47" t="n"/>
@@ -3967,12 +3967,12 @@
       </c>
       <c r="F27" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G27" s="52" t="inlineStr">
         <is>
-          <t>No OAuth response modes.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H27" s="52" t="n"/>
@@ -4003,12 +4003,12 @@
       </c>
       <c r="F28" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G28" s="47" t="inlineStr">
         <is>
-          <t>No pushed authorization requests.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H28" s="47" t="n"/>
@@ -4039,12 +4039,12 @@
       </c>
       <c r="F29" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G29" s="52" t="inlineStr">
         <is>
-          <t>No OAuth sender-constrained tokens.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H29" s="52" t="n"/>
@@ -4075,12 +4075,12 @@
       </c>
       <c r="F30" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G30" s="47" t="inlineStr">
         <is>
-          <t>No OAuth authorization_details parameter.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H30" s="47" t="n"/>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="F31" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G31" s="52" t="inlineStr">
         <is>
-          <t>No OAuth confidential clients.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H31" s="52" t="n"/>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="F33" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G33" s="47" t="inlineStr">
         <is>
-          <t>No OIDC implemented.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H33" s="47" t="n"/>
@@ -4201,12 +4201,12 @@
       </c>
       <c r="F34" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G34" s="52" t="inlineStr">
         <is>
-          <t>No OIDC implemented.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H34" s="52" t="n"/>
@@ -4237,12 +4237,12 @@
       </c>
       <c r="F35" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G35" s="47" t="inlineStr">
         <is>
-          <t>No OIDC implemented.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H35" s="47" t="n"/>
@@ -4273,12 +4273,12 @@
       </c>
       <c r="F36" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G36" s="52" t="inlineStr">
         <is>
-          <t>No OIDC implemented.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H36" s="52" t="n"/>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="F37" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G37" s="47" t="inlineStr">
         <is>
-          <t>No OIDC back-channel logout.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H37" s="47" t="n"/>
@@ -4363,12 +4363,12 @@
       </c>
       <c r="F39" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G39" s="47" t="inlineStr">
         <is>
-          <t>No OpenID Provider.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H39" s="47" t="n"/>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="F40" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G40" s="52" t="inlineStr">
         <is>
-          <t>No OpenID Provider.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H40" s="52" t="n"/>
@@ -4453,12 +4453,12 @@
       </c>
       <c r="F42" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G42" s="47" t="inlineStr">
         <is>
-          <t>No OAuth consent management.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H42" s="47" t="n"/>
@@ -4489,12 +4489,12 @@
       </c>
       <c r="F43" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G43" s="52" t="inlineStr">
         <is>
-          <t>No OAuth consent management.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H43" s="52" t="n"/>
@@ -4525,12 +4525,12 @@
       </c>
       <c r="F44" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G44" s="47" t="inlineStr">
         <is>
-          <t>No OAuth consent management.</t>
+          <t>SecureMarket uses self-issued JWTs with first-party email/password login; there is no OAuth2/OIDC authorization server, OAuth client, or delegated resource-server flow.</t>
         </is>
       </c>
       <c r="H44" s="47" t="n"/>
@@ -4664,12 +4664,12 @@
       </c>
       <c r="F3" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G3" s="47" t="inlineStr">
         <is>
-          <t>SR-AUTH-06: Key management policy defined; JWT secrets loaded from environment variables only; rotation process documented.</t>
+          <t>Secrets-via-environment is documented (core/config.py, report); a formal key-management lifecycle/rotation policy (NIST SP 800-57) is not documented.</t>
         </is>
       </c>
       <c r="H3" s="47" t="n"/>
@@ -4700,12 +4700,12 @@
       </c>
       <c r="F4" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G4" s="52" t="inlineStr">
         <is>
-          <t>Formal cryptographic inventory not maintained in Phase 1; documented in security requirements.</t>
+          <t>The report describes the crypto in use (bcrypt, HS256, SHA-256, TLS); a maintained formal cryptographic inventory is not kept.</t>
         </is>
       </c>
       <c r="H4" s="52" t="n"/>
@@ -4736,12 +4736,12 @@
       </c>
       <c r="F5" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="G5" s="47" t="inlineStr">
         <is>
-          <t>Automated cryptographic discovery not implemented.</t>
+          <t>No automated cryptographic discovery mechanism.</t>
         </is>
       </c>
       <c r="H5" s="47" t="n"/>
@@ -4772,12 +4772,12 @@
       </c>
       <c r="F6" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="G6" s="52" t="inlineStr">
         <is>
-          <t>Post-quantum migration plan not applicable for Phase 1.</t>
+          <t>No documented PQC migration plan.</t>
         </is>
       </c>
       <c r="H6" s="52" t="n"/>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="F8" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G8" s="47" t="inlineStr">
         <is>
-          <t>bcrypt via passlib, SHA-256 via hashlib, HS256 via python-jose — all industry-standard libraries.</t>
+          <t>Industry-standard implementations used: bcrypt, PyJWT, hashlib, OpenSSL (TLS via nginx).</t>
         </is>
       </c>
       <c r="H8" s="47" t="n"/>
@@ -4862,12 +4862,12 @@
       </c>
       <c r="F9" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G9" s="52" t="inlineStr">
         <is>
-          <t>Crypto agility not explicitly designed; algorithm changes require code updates.</t>
+          <t>JWT algorithm is configurable via settings and password hashing is swappable; no full crypto-agility framework.</t>
         </is>
       </c>
       <c r="H9" s="52" t="n"/>
@@ -4898,12 +4898,12 @@
       </c>
       <c r="F10" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G10" s="47" t="inlineStr">
         <is>
-          <t>SR-AUTH-06: 256-bit minimum secret for HS256 (128-bit security). SHA-256 used for file integrity.</t>
+          <t>bcrypt and HS256 (&gt;=256-bit secret expected) plus AES-GCM TLS provide &gt;=128-bit security.</t>
         </is>
       </c>
       <c r="H10" s="47" t="n"/>
@@ -4934,12 +4934,12 @@
       </c>
       <c r="F11" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G11" s="52" t="inlineStr">
         <is>
-          <t>bcrypt.checkpw() performs constant-time comparison to prevent timing attacks.</t>
+          <t>Constant-time password verification (bcrypt.checkpw, dummy-hash fallback for unknown users) prevents timing enumeration.</t>
         </is>
       </c>
       <c r="H11" s="52" t="n"/>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="F12" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G12" s="47" t="inlineStr">
         <is>
-          <t>Cryptographic errors caught and return generic error messages per SR-LOG-05.</t>
+          <t>Crypto failures fail closed: malformed hash -&gt; False; invalid token -&gt; 401.</t>
         </is>
       </c>
       <c r="H12" s="47" t="n"/>
@@ -5024,12 +5024,12 @@
       </c>
       <c r="F14" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G14" s="47" t="inlineStr">
         <is>
-          <t>TLS configured with approved cipher suites via Nginx; no ECB or PKCS#1 v1.5 padding used.</t>
+          <t>No app-level symmetric encryption; TLS uses GCM (no ECB/weak padding).</t>
         </is>
       </c>
       <c r="H14" s="47" t="n"/>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="F15" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G15" s="52" t="inlineStr">
         <is>
-          <t>SR-COMM-01: TLS 1.2+ with approved cipher suites; AES-GCM used in TLS.</t>
+          <t>nginx enables only AES-GCM and CHACHA20-POLY1305 cipher suites.</t>
         </is>
       </c>
       <c r="H15" s="52" t="n"/>
@@ -5096,12 +5096,12 @@
       </c>
       <c r="F16" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G16" s="47" t="inlineStr">
         <is>
-          <t>SR-DATA-02: SHA-256 integrity hashes computed for all files; TLS protects data in transit.</t>
+          <t>Data in transit protected by AEAD (TLS GCM); tokens protected by HMAC (HS256).</t>
         </is>
       </c>
       <c r="H16" s="47" t="n"/>
@@ -5132,12 +5132,12 @@
       </c>
       <c r="F17" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G17" s="52" t="inlineStr">
         <is>
-          <t>JWT jti claim provides unique identifier per token; nonce reuse prevented.</t>
+          <t>Nonce/IV handling is delegated to TLS; no app-level IV reuse.</t>
         </is>
       </c>
       <c r="H17" s="52" t="n"/>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="F18" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G18" s="47" t="inlineStr">
         <is>
-          <t>Using AEAD via TLS; separate encrypt-then-MAC not applicable.</t>
+          <t>AEAD (GCM) is used; no separate encrypt+MAC composition exists to order.</t>
         </is>
       </c>
       <c r="H18" s="47" t="n"/>
@@ -5222,12 +5222,12 @@
       </c>
       <c r="F20" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G20" s="47" t="inlineStr">
         <is>
-          <t>SHA-256 used for file integrity (SR-DATA-02); bcrypt for passwords. No MD5 or SHA-1 used.</t>
+          <t>SHA-256 used for integrity and reset-token hashing; SHA-1 is used only for the HIBP k-anonymity range query (not for security), and is documented.</t>
         </is>
       </c>
       <c r="H20" s="47" t="n"/>
@@ -5258,12 +5258,12 @@
       </c>
       <c r="F21" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G21" s="52" t="inlineStr">
         <is>
-          <t>SR-AUTH-02: bcrypt with minimum cost factor 12 used for password storage.</t>
+          <t>Passwords hashed with bcrypt (per-password salt) - a computationally intensive password hashing function (SR-AUTH-02).</t>
         </is>
       </c>
       <c r="H21" s="52" t="n"/>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="F22" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G22" s="47" t="inlineStr">
         <is>
-          <t>SHA-256 (256-bit output) used for file integrity verification (SR-DATA-02).</t>
+          <t>SHA-256 (256-bit) used for file/invoice integrity and within HS256.</t>
         </is>
       </c>
       <c r="H22" s="47" t="n"/>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="F23" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G23" s="52" t="inlineStr">
         <is>
-          <t>bcrypt with cost factor 12 provides appropriate key stretching for password hashing.</t>
+          <t>bcrypt provides key stretching when deriving from passwords.</t>
         </is>
       </c>
       <c r="H23" s="52" t="n"/>
@@ -5384,12 +5384,12 @@
       </c>
       <c r="F25" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G25" s="47" t="inlineStr">
         <is>
-          <t>Python secrets module and UUID v4 (SR-AUTHZ-08) used for secure random generation.</t>
+          <t>Reset tokens use secrets.token_urlsafe(32) (CSPRNG, 256-bit). Resource identifiers use uuid4 (acknowledged as identifiers, not secrets).</t>
         </is>
       </c>
       <c r="H25" s="47" t="n"/>
@@ -5420,12 +5420,12 @@
       </c>
       <c r="F26" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G26" s="52" t="inlineStr">
         <is>
-          <t>Python secrets module uses OS CSPRNG; designed to work securely under load.</t>
+          <t>Randomness sourced from the OS CSPRNG (secrets/os.urandom).</t>
         </is>
       </c>
       <c r="H26" s="52" t="n"/>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="F28" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G28" s="47" t="inlineStr">
         <is>
-          <t>SR-AUTH-06: HS256 with 256-bit secret or RS256 used; no vulnerable key generation.</t>
+          <t>HMAC-SHA256 (HS256) for tokens; TLS certificate key generation handled by the PKI/Let's Encrypt.</t>
         </is>
       </c>
       <c r="H28" s="47" t="n"/>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="F29" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G29" s="52" t="inlineStr">
         <is>
-          <t>TLS handles key exchange using approved Diffie-Hellman parameters via Nginx.</t>
+          <t>TLS 1.2/1.3 with ECDHE key exchange (forward secrecy) configured in nginx.</t>
         </is>
       </c>
       <c r="H29" s="52" t="n"/>
@@ -5564,12 +5564,12 @@
       </c>
       <c r="F31" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="G31" s="47" t="inlineStr">
         <is>
-          <t>Full memory encryption not implemented; OS-level controls assumed.</t>
+          <t>No full-memory/confidential-computing encryption in the deployment model.</t>
         </is>
       </c>
       <c r="H31" s="47" t="n"/>
@@ -5600,12 +5600,12 @@
       </c>
       <c r="F32" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G32" s="52" t="inlineStr">
         <is>
-          <t>SR-DATA-08: Sensitive data (passwords, tokens) not retained in memory beyond processing; not logged.</t>
+          <t>Response schemas limit exposed data; explicit encrypt-immediately-after-use of in-process data is not implemented.</t>
         </is>
       </c>
       <c r="H32" s="52" t="n"/>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="F3" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G3" s="47" t="inlineStr">
         <is>
-          <t>SR-COMM-01: TLS 1.2 and TLS 1.3 enabled; configured in Nginx reverse proxy.</t>
+          <t>nginx enables only TLS 1.2 and 1.3 (SR-COMM-01).</t>
         </is>
       </c>
       <c r="H3" s="47" t="n"/>
@@ -5775,12 +5775,12 @@
       </c>
       <c r="F4" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G4" s="52" t="inlineStr">
         <is>
-          <t>Nginx configured with recommended cipher suites; weak ciphers disabled.</t>
+          <t>Recommended ECDHE AES-GCM / CHACHA20 cipher suites with forward secrecy configured in nginx.</t>
         </is>
       </c>
       <c r="H4" s="52" t="n"/>
@@ -5811,12 +5811,12 @@
       </c>
       <c r="F5" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G5" s="47" t="inlineStr">
         <is>
-          <t>mTLS client certificates not used; JWT authentication used instead.</t>
+          <t>No mutual-TLS client-certificate authentication in scope.</t>
         </is>
       </c>
       <c r="H5" s="47" t="n"/>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="F6" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="G6" s="52" t="inlineStr">
         <is>
-          <t>OCSP Stapling not configured in Phase 1 design.</t>
+          <t>OCSP stapling / revocation checking not configured.</t>
         </is>
       </c>
       <c r="H6" s="52" t="n"/>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="F7" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="G7" s="47" t="inlineStr">
         <is>
-          <t>Encrypted Client Hello not configured in Phase 1.</t>
+          <t>Encrypted Client Hello (ECH) not configured.</t>
         </is>
       </c>
       <c r="H7" s="47" t="n"/>
@@ -5937,12 +5937,12 @@
       </c>
       <c r="F9" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G9" s="47" t="inlineStr">
         <is>
-          <t>SR-COMM-01: All client-server communication uses HTTPS/TLS; no HTTP fallback.</t>
+          <t>All client traffic is HTTPS; HTTP is 301-redirected; no plaintext fallback (SR-COMM-01).</t>
         </is>
       </c>
       <c r="H9" s="47" t="n"/>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="F10" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G10" s="52" t="inlineStr">
         <is>
-          <t>Nginx configured with publicly trusted TLS certificate.</t>
+          <t>nginx is configured for Let's Encrypt (ACME HTTP-01) publicly trusted certificates in production; self-signed only for dev.</t>
         </is>
       </c>
       <c r="H10" s="52" t="n"/>
@@ -6027,12 +6027,12 @@
       </c>
       <c r="F12" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G12" s="47" t="inlineStr">
         <is>
-          <t>SR-COMM-03: Database connections use TLS (sslmode=require); all internal communications encrypted.</t>
+          <t>Client-facing TLS enforced and outbound HIBP call uses HTTPS; the app-&gt;PostgreSQL connection does not enforce sslmode=require (SR-COMM-03 not implemented).</t>
         </is>
       </c>
       <c r="H12" s="47" t="n"/>
@@ -6063,12 +6063,12 @@
       </c>
       <c r="F13" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G13" s="52" t="inlineStr">
         <is>
-          <t>SR-COMM-03: sslmode=require validates PostgreSQL server certificate.</t>
+          <t>httpx validates the HIBP server certificate; DB-side TLS is not enabled.</t>
         </is>
       </c>
       <c r="H13" s="52" t="n"/>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="F14" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G14" s="47" t="inlineStr">
         <is>
-          <t>SR-COMM-03: Internal API-to-database communication uses TLS.</t>
+          <t>nginx-&gt;app traffic is plaintext HTTP over the isolated internal Docker network (app not exposed); internal TLS is not used.</t>
         </is>
       </c>
       <c r="H14" s="47" t="n"/>
@@ -6135,12 +6135,12 @@
       </c>
       <c r="F15" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G15" s="52" t="inlineStr">
         <is>
-          <t>PostgreSQL TLS configured with trusted CA certificates.</t>
+          <t>Follows from V12.3.3: internal service-to-service traffic is not TLS, so no internal trusted-cert validation is performed.</t>
         </is>
       </c>
       <c r="H15" s="52" t="n"/>
@@ -6171,12 +6171,12 @@
       </c>
       <c r="F16" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="G16" s="47" t="inlineStr">
         <is>
-          <t>Single-service deployment on Docker network; no inter-service mTLS required.</t>
+          <t>No intra-service strong authentication (mTLS/service mesh).</t>
         </is>
       </c>
       <c r="H16" s="47" t="n"/>
@@ -6310,12 +6310,12 @@
       </c>
       <c r="F3" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G3" s="47" t="inlineStr">
         <is>
-          <t>Architecture section documents all communication needs: client-API, API-database, API-filesystem.</t>
+          <t>The report documents external dependencies (PostgreSQL, HIBP) and the data flows/communication needs.</t>
         </is>
       </c>
       <c r="H3" s="47" t="n"/>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="F4" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G4" s="52" t="inlineStr">
         <is>
-          <t>Connection pool limits and behavior not explicitly documented.</t>
+          <t>A DB connection pool is configured (pool_size 5, max_overflow 10, pool_recycle 1800) but behavior at the limit is not documented.</t>
         </is>
       </c>
       <c r="H4" s="52" t="n"/>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="F5" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G5" s="47" t="inlineStr">
         <is>
-          <t>Resource management strategies not fully documented in Phase 1.</t>
+          <t>HIBP call has a 5s timeout and fails open; pool_recycle set; resource-management strategy is not fully documented.</t>
         </is>
       </c>
       <c r="H5" s="47" t="n"/>
@@ -6418,12 +6418,12 @@
       </c>
       <c r="F6" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G6" s="52" t="inlineStr">
         <is>
-          <t>Secret rotation schedule not formally documented.</t>
+          <t>Critical secrets are identified (SECRET_KEY, DATABASE_URL); a rotation schedule is not documented.</t>
         </is>
       </c>
       <c r="H6" s="52" t="n"/>
@@ -6472,12 +6472,12 @@
       </c>
       <c r="F8" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G8" s="47" t="inlineStr">
         <is>
-          <t>SR-LOG-02: Separate audit_log DB user with INSERT/SELECT only. Application DB user with minimum required privileges.</t>
+          <t>DB auth uses a dedicated service credential from env (not default); certificate/short-lived-token service auth is not used.</t>
         </is>
       </c>
       <c r="H8" s="47" t="n"/>
@@ -6508,12 +6508,12 @@
       </c>
       <c r="F9" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G9" s="52" t="inlineStr">
         <is>
-          <t>SR-LOG-02: Least-privilege DB users (app user: DML only; audit user: INSERT/SELECT only).</t>
+          <t>A single application DB user with full DML is used; the least-privilege split (separate INSERT/SELECT-only audit user, SR-LOG-02) is designed but not implemented.</t>
         </is>
       </c>
       <c r="H9" s="52" t="n"/>
@@ -6544,12 +6544,12 @@
       </c>
       <c r="F10" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G10" s="47" t="inlineStr">
         <is>
-          <t>No default credentials used; all credentials set via environment variables.</t>
+          <t>App refuses to start without SECRET_KEY/DATABASE_URL; no default credentials (core/config.py); .env.example holds placeholders only.</t>
         </is>
       </c>
       <c r="H10" s="47" t="n"/>
@@ -6580,12 +6580,12 @@
       </c>
       <c r="F11" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G11" s="52" t="inlineStr">
         <is>
-          <t>No outbound connections to user-supplied URLs; all external resources on allowlist.</t>
+          <t>Outbound connections are limited to fixed endpoints (HIBP, DB); no formal network egress allow-list is enforced.</t>
         </is>
       </c>
       <c r="H11" s="52" t="n"/>
@@ -6616,12 +6616,12 @@
       </c>
       <c r="F12" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G12" s="47" t="inlineStr">
         <is>
-          <t>Nginx and Docker network configuration restricts outbound connections.</t>
+          <t>No web/app-server egress allow-list configured; outbound is in practice limited to HIBP and the DB.</t>
         </is>
       </c>
       <c r="H12" s="47" t="n"/>
@@ -6652,12 +6652,12 @@
       </c>
       <c r="F13" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G13" s="52" t="inlineStr">
         <is>
-          <t>Documented connection configuration per service not fully specified in Phase 1.</t>
+          <t>Connection pool/timeout settings exist; not all documented connection behaviors are enforced/verified.</t>
         </is>
       </c>
       <c r="H13" s="52" t="n"/>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="F15" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G15" s="47" t="inlineStr">
         <is>
-          <t>SR-AUTH-06: Secrets managed via environment variables; never hardcoded in source or build artifacts.</t>
+          <t>Secrets are provided via environment variables and .env is excluded from VCS (.gitignore) and the image (.dockerignore); no dedicated secrets vault/HSM is used.</t>
         </is>
       </c>
       <c r="H15" s="47" t="n"/>
@@ -6742,12 +6742,12 @@
       </c>
       <c r="F16" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G16" s="52" t="inlineStr">
         <is>
-          <t>Environment variables accessible only to application process; principle of least privilege applied.</t>
+          <t>Secrets are scoped to the container environment; access is not managed by a least-privilege secrets solution.</t>
         </is>
       </c>
       <c r="H16" s="52" t="n"/>
@@ -6778,12 +6778,12 @@
       </c>
       <c r="F17" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="G17" s="47" t="inlineStr">
         <is>
-          <t>Hardware Security Module not used; environment-variable-based secret management used.</t>
+          <t>No isolated security module/HSM for cryptographic operations.</t>
         </is>
       </c>
       <c r="H17" s="47" t="n"/>
@@ -6814,12 +6814,12 @@
       </c>
       <c r="F18" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="G18" s="52" t="inlineStr">
         <is>
-          <t>Automated secret rotation not implemented in Phase 1.</t>
+          <t>No automatic secret expiry/rotation.</t>
         </is>
       </c>
       <c r="H18" s="52" t="n"/>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="F20" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G20" s="47" t="inlineStr">
         <is>
-          <t>Docker build process excludes .git directory; source metadata not deployed to production.</t>
+          <t>.dockerignore excludes .git and .github from the production image.</t>
         </is>
       </c>
       <c r="H20" s="47" t="n"/>
@@ -6904,12 +6904,12 @@
       </c>
       <c r="F21" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G21" s="52" t="inlineStr">
         <is>
-          <t>FastAPI debug mode disabled in production; no debug endpoints exposed.</t>
+          <t>Production disables Swagger /docs and ReDoc (main.py) and runs without debug mode.</t>
         </is>
       </c>
       <c r="H21" s="52" t="n"/>
@@ -6940,12 +6940,12 @@
       </c>
       <c r="F22" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G22" s="47" t="inlineStr">
         <is>
-          <t>SR-DATA-03: Files not in web root; no directory listings possible.</t>
+          <t>No directory listing: nginx autoindex is off and the app exposes no listing.</t>
         </is>
       </c>
       <c r="H22" s="47" t="n"/>
@@ -6976,12 +6976,12 @@
       </c>
       <c r="F23" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G23" s="52" t="inlineStr">
         <is>
-          <t>Nginx configured to disable HTTP TRACE method.</t>
+          <t>Only declared routes are served; HTTP TRACE is not handled (nginx/uvicorn).</t>
         </is>
       </c>
       <c r="H23" s="52" t="n"/>
@@ -7012,12 +7012,12 @@
       </c>
       <c r="F24" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G24" s="47" t="inlineStr">
         <is>
-          <t>FastAPI OpenAPI docs (/docs, /redoc) disabled in production configuration.</t>
+          <t>/docs and ReDoc disabled in production; no monitoring endpoints exposed; health route returns minimal data.</t>
         </is>
       </c>
       <c r="H24" s="47" t="n"/>
@@ -7048,12 +7048,12 @@
       </c>
       <c r="F25" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G25" s="52" t="inlineStr">
         <is>
-          <t>SR-LOG-05: Error responses return generic messages; no version information exposed.</t>
+          <t>nginx server_tokens off; framework/server version details are not disclosed.</t>
         </is>
       </c>
       <c r="H25" s="52" t="n"/>
@@ -7084,12 +7084,12 @@
       </c>
       <c r="F26" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G26" s="47" t="inlineStr">
         <is>
-          <t>Files served through authenticated API endpoints only; web server does not serve files directly.</t>
+          <t>The web tier proxies to the app; no arbitrary static file serving - only validated UUID image files are returned by the API.</t>
         </is>
       </c>
       <c r="H26" s="47" t="n"/>
@@ -7223,12 +7223,12 @@
       </c>
       <c r="F3" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G3" s="47" t="inlineStr">
         <is>
-          <t>SR-DATA-08: Sensitive data identified and classified (passwords, tokens, addresses, file contents).</t>
+          <t>The Phase 1 report identifies and classifies sensitive data (credentials, tokens, PII, order/financial data).</t>
         </is>
       </c>
       <c r="H3" s="47" t="n"/>
@@ -7259,12 +7259,12 @@
       </c>
       <c r="F4" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G4" s="52" t="inlineStr">
         <is>
-          <t>SR-DATA-01 to SR-DATA-10: Protection requirements documented for each data category.</t>
+          <t>Protection requirements are described across SR-DATA/SR-LOG; a formal per-protection-level requirements matrix is not maintained.</t>
         </is>
       </c>
       <c r="H4" s="52" t="n"/>
@@ -7313,12 +7313,12 @@
       </c>
       <c r="F6" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G6" s="47" t="inlineStr">
         <is>
-          <t>Credentials and tokens sent in Authorization header or request body; never in URL or query string.</t>
+          <t>JWTs are carried in the Authorization header; credentials/tokens are sent in the request body, never in URL/query strings.</t>
         </is>
       </c>
       <c r="H6" s="47" t="n"/>
@@ -7349,12 +7349,12 @@
       </c>
       <c r="F7" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G7" s="52" t="inlineStr">
         <is>
-          <t>SR-COMM-05: Cache-Control: no-store set on authenticated responses.</t>
+          <t>No server-side caching of API responses; explicit Cache-Control: no-store on authenticated responses (SR-COMM-05) is not set.</t>
         </is>
       </c>
       <c r="H7" s="52" t="n"/>
@@ -7385,12 +7385,12 @@
       </c>
       <c r="F8" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G8" s="47" t="inlineStr">
         <is>
-          <t>No third-party analytics, tracking, or data sharing integrations.</t>
+          <t>No analytics/trackers; the only third-party call is the HIBP k-anonymity query (only a 5-char SHA-1 prefix leaves the server).</t>
         </is>
       </c>
       <c r="H8" s="47" t="n"/>
@@ -7421,12 +7421,12 @@
       </c>
       <c r="F9" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G9" s="52" t="inlineStr">
         <is>
-          <t>SR-DATA-01 to SR-DATA-10: Encryption, integrity, retention, and access controls implemented per documented requirements.</t>
+          <t>Core controls implemented (bcrypt, TLS, secrets not logged); not every per-level control (e.g. DB-level encryption) is in place.</t>
         </is>
       </c>
       <c r="H9" s="52" t="n"/>
@@ -7457,12 +7457,12 @@
       </c>
       <c r="F10" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G10" s="47" t="inlineStr">
         <is>
-          <t>SR-COMM-05: Cache-Control: no-store prevents caching of sensitive responses.</t>
+          <t>No caching layer is configured; nginx returns proper 404s, but web-cache-deception hardening is not explicitly configured.</t>
         </is>
       </c>
       <c r="H10" s="47" t="n"/>
@@ -7493,12 +7493,12 @@
       </c>
       <c r="F11" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G11" s="52" t="inlineStr">
         <is>
-          <t>Pydantic response schemas return only required fields; no full object dumps.</t>
+          <t>Response schemas exclude secrets (no password hash returned); field-level masking (e.g. partial email) is not implemented.</t>
         </is>
       </c>
       <c r="H11" s="52" t="n"/>
@@ -7529,12 +7529,12 @@
       </c>
       <c r="F12" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="G12" s="47" t="inlineStr">
         <is>
-          <t>SR-LOG-06: Audit logs retained for 12 months; no indefinite data retention.</t>
+          <t>Blacklist/reset-token cleanup is noted as a future periodic job; no automated retention/deletion is implemented.</t>
         </is>
       </c>
       <c r="H12" s="47" t="n"/>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="F13" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="G13" s="52" t="inlineStr">
         <is>
-          <t>SR-DATA-01: UUID filenames used; original filenames and EXIF metadata not exposed in API responses.</t>
+          <t>EXIF/metadata is not stripped from uploaded images.</t>
         </is>
       </c>
       <c r="H13" s="52" t="n"/>
@@ -7619,12 +7619,12 @@
       </c>
       <c r="F15" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G15" s="47" t="inlineStr">
         <is>
-          <t>SR-AUTH-08: Refresh tokens invalidated on logout; access tokens expire after 15 minutes.</t>
+          <t>No cookies/browser storage are used by the API; client-side token disposal is the client's responsibility.</t>
         </is>
       </c>
       <c r="H15" s="47" t="n"/>
@@ -7655,12 +7655,12 @@
       </c>
       <c r="F16" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G16" s="52" t="inlineStr">
         <is>
-          <t>SR-COMM-05: Cache-Control: no-store set on all authenticated responses.</t>
+          <t>Cache-Control: no-store on sensitive responses (SR-COMM-05) is designed but not yet set by the app.</t>
         </is>
       </c>
       <c r="H16" s="52" t="n"/>
@@ -7691,12 +7691,12 @@
       </c>
       <c r="F17" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G17" s="47" t="inlineStr">
         <is>
-          <t>REST API; no browser storage used. JWT tokens managed by API clients.</t>
+          <t>The API does not use browser storage.</t>
         </is>
       </c>
       <c r="H17" s="47" t="n"/>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="F3" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G3" s="47" t="inlineStr">
         <is>
-          <t>SR-3RD-02: CI/CD pipeline scans dependencies; builds fail on critical CVEs. Remediation enforced.</t>
+          <t>CI fails builds on dependency CVEs (pip-audit, sca-scan.yml); a formal risk-based remediation SLA is not documented.</t>
         </is>
       </c>
       <c r="H3" s="47" t="n"/>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="F4" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G4" s="52" t="inlineStr">
         <is>
-          <t>SR-3RD-03: SBOM generated per release using CycloneDX/SPDX.</t>
+          <t>A CycloneDX SBOM is generated in CI (sbom-cyclonedx.yml); dependencies are sourced from PyPI.</t>
         </is>
       </c>
       <c r="H4" s="52" t="n"/>
@@ -7902,12 +7902,12 @@
       </c>
       <c r="F5" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G5" s="47" t="inlineStr">
         <is>
-          <t>Time-consuming functionality (file uploads, exports) not formally documented with availability strategies in Phase 1.</t>
+          <t>Resource-heavy features (uploads, invoice generation) are identified informally; a formal availability strategy (queues/async) is not documented.</t>
         </is>
       </c>
       <c r="H5" s="47" t="n"/>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="F6" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="G6" s="52" t="inlineStr">
         <is>
-          <t>SR-3RD: Third-party libraries reviewed; risky components identified in security requirements.</t>
+          <t>No documentation flags specific 'risky' third-party libraries.</t>
         </is>
       </c>
       <c r="H6" s="52" t="n"/>
@@ -7974,12 +7974,12 @@
       </c>
       <c r="F7" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G7" s="47" t="inlineStr">
         <is>
-          <t>Architecture section documents dangerous functionality: Jinja2 templates, filesystem operations, file uploads.</t>
+          <t>The report notes file handling/PDF generation as sensitive; a formal 'dangerous functionality' catalogue is not maintained.</t>
         </is>
       </c>
       <c r="H7" s="47" t="n"/>
@@ -8028,12 +8028,12 @@
       </c>
       <c r="F9" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G9" s="47" t="inlineStr">
         <is>
-          <t>SR-3RD-01: All dependencies pinned; SR-3RD-02: CI/CD blocks builds with unpatched critical CVEs.</t>
+          <t>The pip-audit gate fails the build on any CVE in requirements (sca-scan.yml).</t>
         </is>
       </c>
       <c r="H9" s="47" t="n"/>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="F10" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G10" s="52" t="inlineStr">
         <is>
-          <t>SR-INPUT-08: Pagination limits prevent resource exhaustion. SR-AUTH-09: Rate limiting protects against DoS.</t>
+          <t>Upload size limits, quotas and pagination defaults exist; per-endpoint rate limiting against resource exhaustion is not implemented.</t>
         </is>
       </c>
       <c r="H10" s="52" t="n"/>
@@ -8100,12 +8100,12 @@
       </c>
       <c r="F11" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G11" s="47" t="inlineStr">
         <is>
-          <t>SR-3RD-05: No dev/debug dependencies in production Docker image.</t>
+          <t>tests/ and dev dependencies are excluded from the image and /docs is disabled in prod; however test_debug.py at the app root is not excluded by .dockerignore.</t>
         </is>
       </c>
       <c r="H11" s="47" t="n"/>
@@ -8136,12 +8136,12 @@
       </c>
       <c r="F12" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G12" s="52" t="inlineStr">
         <is>
-          <t>SR-3RD-01: Dependencies pinned to specific versions from PyPI; dependency confusion risk mitigated.</t>
+          <t>Dependencies come from public PyPI with an SBOM; requirements use &gt;= ranges (no pinned versions/hashes), leaving some dependency-confusion/drift risk.</t>
         </is>
       </c>
       <c r="H12" s="52" t="n"/>
@@ -8172,12 +8172,12 @@
       </c>
       <c r="F13" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G13" s="47" t="inlineStr">
         <is>
-          <t>SR-INPUT-05: Jinja2 SandboxedEnvironment isolates template execution. SR-DATA-03: Files outside web root.</t>
+          <t>App runs as a non-root user in a container on an isolated network; DB and app are not published to the host.</t>
         </is>
       </c>
       <c r="H13" s="47" t="n"/>
@@ -8226,12 +8226,12 @@
       </c>
       <c r="F15" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G15" s="47" t="inlineStr">
         <is>
-          <t>Pydantic response schemas return only required fields; sensitive fields excluded from API responses.</t>
+          <t>Response Pydantic schemas return only required fields (e.g. UserResponse omits the password hash).</t>
         </is>
       </c>
       <c r="H15" s="47" t="n"/>
@@ -8262,12 +8262,12 @@
       </c>
       <c r="F16" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G16" s="52" t="inlineStr">
         <is>
-          <t>No backend HTTP calls to user-supplied URLs; no redirect following from user input.</t>
+          <t>The only backend HTTP client (httpx for HIBP) does not follow redirects by default.</t>
         </is>
       </c>
       <c r="H16" s="52" t="n"/>
@@ -8298,12 +8298,12 @@
       </c>
       <c r="F17" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G17" s="47" t="inlineStr">
         <is>
-          <t>Pydantic schemas define explicit allowed fields per endpoint; mass assignment prevented.</t>
+          <t>Input schemas restrict assignable fields (UserUpdate cannot set role/is_active; order prices are server-snapshotted), mitigating mass assignment (T-P2-03).</t>
         </is>
       </c>
       <c r="H17" s="47" t="n"/>
@@ -8334,12 +8334,12 @@
       </c>
       <c r="F18" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G18" s="52" t="inlineStr">
         <is>
-          <t>Nginx passes X-Real-IP header; application uses trusted proxy IP for rate limiting and logging.</t>
+          <t>nginx forwards X-Real-IP/X-Forwarded-For; the app does not yet use client IP for security decisions (rate limiting pending). --forwarded-allow-ips is broad but the app is proxy-only.</t>
         </is>
       </c>
       <c r="H18" s="52" t="n"/>
@@ -8370,12 +8370,12 @@
       </c>
       <c r="F19" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G19" s="47" t="inlineStr">
         <is>
-          <t>SR-INPUT-01: Pydantic strict type checking enforced; type coercion disabled.</t>
+          <t>Pydantic enforces strict typing and enums (OrderStatus/ProductStatus); Python uses strict equality (no type juggling).</t>
         </is>
       </c>
       <c r="H19" s="47" t="n"/>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="F20" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G20" s="52" t="inlineStr">
         <is>
-          <t>Python backend; no JavaScript prototype pollution risk.</t>
+          <t>No JavaScript; prototype pollution not applicable.</t>
         </is>
       </c>
       <c r="H20" s="52" t="n"/>
@@ -8442,12 +8442,12 @@
       </c>
       <c r="F21" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G21" s="47" t="inlineStr">
         <is>
-          <t>FastAPI distinguishes between path, query, and body parameters; HTTP parameter pollution prevented.</t>
+          <t>FastAPI binds parameters by declared source and type, avoiding ambiguous multi-source parameter handling (HPP).</t>
         </is>
       </c>
       <c r="H21" s="47" t="n"/>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="F23" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G23" s="47" t="inlineStr">
         <is>
-          <t>SR-DATA-10: SQLAlchemy SELECT FOR UPDATE provides thread-safe stock operations.</t>
+          <t>Per-request SQLAlchemy sessions; no shared mutable in-memory state across requests.</t>
         </is>
       </c>
       <c r="H23" s="47" t="n"/>
@@ -8532,12 +8532,12 @@
       </c>
       <c r="F24" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G24" s="52" t="inlineStr">
         <is>
-          <t>SR-DATA-10: Check-and-decrement stock performed atomically within database transaction.</t>
+          <t>Image writes are atomic (temp+rename, symlink rejection); the stock check-then-decrement is not atomic (TOCTOU/race, SR-DATA-10 pending).</t>
         </is>
       </c>
       <c r="H24" s="52" t="n"/>
@@ -8568,12 +8568,12 @@
       </c>
       <c r="F25" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G25" s="47" t="inlineStr">
         <is>
-          <t>SQLAlchemy transaction management ensures lock consistency within session scope.</t>
+          <t>No application-level locking is used where it matters (stock decrement); to be addressed with DB row-level locking.</t>
         </is>
       </c>
       <c r="H25" s="47" t="n"/>
@@ -8604,12 +8604,12 @@
       </c>
       <c r="F26" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G26" s="52" t="inlineStr">
         <is>
-          <t>SQLAlchemy connection pool with max_overflow limit ensures fair resource allocation.</t>
+          <t>uvicorn workers plus a bounded DB connection pool exist; no per-user fairness/anti-starvation controls.</t>
         </is>
       </c>
       <c r="H26" s="52" t="n"/>
@@ -8743,12 +8743,12 @@
       </c>
       <c r="F3" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G3" s="47" t="inlineStr">
         <is>
-          <t>SR-LOG-01, SR-LOG-03: Audit log inventory defined; events, format, storage, access controls, and retention documented.</t>
+          <t>Logging is described in the report (SR-LOG); a formal log inventory (events/formats/storage/retention) is not maintained, and the immutable audit-log table (SR-LOG-01/02) is designed but not implemented.</t>
         </is>
       </c>
       <c r="H3" s="47" t="n"/>
@@ -8797,12 +8797,12 @@
       </c>
       <c r="F5" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G5" s="47" t="inlineStr">
         <is>
-          <t>SR-LOG-01: Each log entry includes user ID, action, target resource, timestamp, IP address, and result.</t>
+          <t>Auth/authz events are logged with user id and action (auth_service.py, middleware/auth.py); IP address is not consistently captured (no IP/rate-limit middleware) - SR-AUTH-10 partially met.</t>
         </is>
       </c>
       <c r="H5" s="47" t="n"/>
@@ -8833,12 +8833,12 @@
       </c>
       <c r="F6" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G6" s="52" t="inlineStr">
         <is>
-          <t>UTC timestamps used in all audit log entries for consistency.</t>
+          <t>Application timestamps are timezone-aware UTC (datetime.now(timezone.utc)).</t>
         </is>
       </c>
       <c r="H6" s="52" t="n"/>
@@ -8869,12 +8869,12 @@
       </c>
       <c r="F7" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G7" s="47" t="inlineStr">
         <is>
-          <t>SR-LOG-01: Application logs only to the documented audit log; no undocumented log destinations.</t>
+          <t>Logs are written to container stdout/stderr; sinks are not formally documented in a log inventory.</t>
         </is>
       </c>
       <c r="H7" s="47" t="n"/>
@@ -8905,12 +8905,12 @@
       </c>
       <c r="F8" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G8" s="52" t="inlineStr">
         <is>
-          <t>Structured logging format (JSON) used; machine-readable and correlatable.</t>
+          <t>Standard Python logging to stdout is used; a structured/JSON common format is not configured.</t>
         </is>
       </c>
       <c r="H8" s="52" t="n"/>
@@ -8941,12 +8941,12 @@
       </c>
       <c r="F9" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G9" s="47" t="inlineStr">
         <is>
-          <t>SR-LOG-04, SR-DATA-08: Passwords, tokens, and file contents never logged; sensitive fields masked.</t>
+          <t>Logging avoids secrets - only user ids/actions are logged; passwords/tokens are never logged (SR-LOG-04, SR-DATA-08).</t>
         </is>
       </c>
       <c r="H9" s="47" t="n"/>
@@ -8995,12 +8995,12 @@
       </c>
       <c r="F11" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G11" s="47" t="inlineStr">
         <is>
-          <t>SR-AUTH-10, SR-LOG-03: All authentication attempts (success and failure) logged with metadata.</t>
+          <t>Login success and account lockout are logged; per-attempt failed logins are not individually logged (and without IP).</t>
         </is>
       </c>
       <c r="H11" s="47" t="n"/>
@@ -9031,12 +9031,12 @@
       </c>
       <c r="F12" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G12" s="52" t="inlineStr">
         <is>
-          <t>SR-AUTHZ-07, SR-LOG-03: All authorization failures logged. Access to sensitive data logged.</t>
+          <t>Authorization failures are logged: RBAC denials and token/JWT denials in middleware/auth.py.</t>
         </is>
       </c>
       <c r="H12" s="52" t="n"/>
@@ -9067,12 +9067,12 @@
       </c>
       <c r="F13" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G13" s="47" t="inlineStr">
         <is>
-          <t>SR-LOG-03: Comprehensive event logging including input validation failures and business logic bypasses.</t>
+          <t>Auth/authz events are logged; input-validation failures (FastAPI 422) and anti-automation bypass attempts are not explicitly logged.</t>
         </is>
       </c>
       <c r="H13" s="47" t="n"/>
@@ -9103,12 +9103,12 @@
       </c>
       <c r="F14" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G14" s="52" t="inlineStr">
         <is>
-          <t>SR-LOG-01: Unexpected errors and security control failures logged to audit log.</t>
+          <t>Auth/JWT errors are logged, but some handlers swallow exceptions silently (e.g. invoice generation in routers/orders.py) without logging.</t>
         </is>
       </c>
       <c r="H14" s="52" t="n"/>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="F16" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G16" s="47" t="inlineStr">
         <is>
-          <t>Structured logging prevents log injection; user input not interpolated directly into log strings.</t>
+          <t>Parameterized logging is used; user-controlled values are not explicitly sanitized for CRLF/log-injection.</t>
         </is>
       </c>
       <c r="H16" s="47" t="n"/>
@@ -9193,12 +9193,12 @@
       </c>
       <c r="F17" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G17" s="52" t="inlineStr">
         <is>
-          <t>SR-LOG-02: Audit log DB user has INSERT and SELECT only; no UPDATE/DELETE permitted.</t>
+          <t>Logs go to container stdout; an immutable/append-only audit store with a restricted DB user (SR-LOG-02) is designed but not implemented.</t>
         </is>
       </c>
       <c r="H17" s="52" t="n"/>
@@ -9229,12 +9229,12 @@
       </c>
       <c r="F18" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="G18" s="47" t="inlineStr">
         <is>
-          <t>Logs stored in same system in Phase 1; separate log transmission to SIEM not implemented.</t>
+          <t>No centralized/separate log-shipping system is configured.</t>
         </is>
       </c>
       <c r="H18" s="47" t="n"/>
@@ -9283,12 +9283,12 @@
       </c>
       <c r="F20" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G20" s="47" t="inlineStr">
         <is>
-          <t>SR-LOG-05: Generic error messages returned; no stack traces, DB errors, or internal paths exposed.</t>
+          <t>HTTPExceptions return generic messages; debug is disabled so no stack traces leak; login returns a uniform 401 (no user enumeration) - SR-LOG-05, NFR-09.</t>
         </is>
       </c>
       <c r="H20" s="47" t="n"/>
@@ -9319,12 +9319,12 @@
       </c>
       <c r="F21" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G21" s="52" t="inlineStr">
         <is>
-          <t>FastAPI exception handlers provide graceful degradation on external service failures.</t>
+          <t>External failures degrade gracefully - the HIBP outage path fails open by design (documented defence-in-depth).</t>
         </is>
       </c>
       <c r="H21" s="52" t="n"/>
@@ -9355,12 +9355,12 @@
       </c>
       <c r="F22" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G22" s="47" t="inlineStr">
         <is>
-          <t>FastAPI global exception handler catches all unhandled exceptions; transactions roll back on error.</t>
+          <t>Security-critical paths fail closed (authn/authz deny on error); validation errors return 422. The HIBP fail-open is a non-primary, defence-in-depth check.</t>
         </is>
       </c>
       <c r="H22" s="47" t="n"/>
@@ -9391,12 +9391,12 @@
       </c>
       <c r="F23" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G23" s="52" t="inlineStr">
         <is>
-          <t>FastAPI global exception handler acts as last-resort handler; prevents application crash on unhandled exceptions.</t>
+          <t>FastAPI's default handler returns a generic 500 for unhandled exceptions; a custom last-resort handler with logging is not registered.</t>
         </is>
       </c>
       <c r="H23" s="52" t="n"/>
@@ -9530,12 +9530,12 @@
       </c>
       <c r="F3" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G3" s="47" t="inlineStr">
         <is>
-          <t>No WebRTC or TURN server in SecureMarket.</t>
+          <t>SecureMarket is a JSON REST API; no WebRTC, TURN/STUN, DTLS-SRTP, or media/signaling servers are used.</t>
         </is>
       </c>
       <c r="H3" s="47" t="n"/>
@@ -9566,12 +9566,12 @@
       </c>
       <c r="F4" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G4" s="52" t="inlineStr">
         <is>
-          <t>No WebRTC or TURN server in SecureMarket.</t>
+          <t>SecureMarket is a JSON REST API; no WebRTC, TURN/STUN, DTLS-SRTP, or media/signaling servers are used.</t>
         </is>
       </c>
       <c r="H4" s="52" t="n"/>
@@ -9620,12 +9620,12 @@
       </c>
       <c r="F6" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G6" s="47" t="inlineStr">
         <is>
-          <t>No WebRTC or DTLS in SecureMarket.</t>
+          <t>SecureMarket is a JSON REST API; no WebRTC, TURN/STUN, DTLS-SRTP, or media/signaling servers are used.</t>
         </is>
       </c>
       <c r="H6" s="47" t="n"/>
@@ -9656,12 +9656,12 @@
       </c>
       <c r="F7" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G7" s="52" t="inlineStr">
         <is>
-          <t>No WebRTC or DTLS in SecureMarket.</t>
+          <t>SecureMarket is a JSON REST API; no WebRTC, TURN/STUN, DTLS-SRTP, or media/signaling servers are used.</t>
         </is>
       </c>
       <c r="H7" s="52" t="n"/>
@@ -9692,12 +9692,12 @@
       </c>
       <c r="F8" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G8" s="47" t="inlineStr">
         <is>
-          <t>No WebRTC or SRTP in SecureMarket.</t>
+          <t>SecureMarket is a JSON REST API; no WebRTC, TURN/STUN, DTLS-SRTP, or media/signaling servers are used.</t>
         </is>
       </c>
       <c r="H8" s="47" t="n"/>
@@ -9728,12 +9728,12 @@
       </c>
       <c r="F9" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G9" s="52" t="inlineStr">
         <is>
-          <t>No WebRTC or SRTP in SecureMarket.</t>
+          <t>SecureMarket is a JSON REST API; no WebRTC, TURN/STUN, DTLS-SRTP, or media/signaling servers are used.</t>
         </is>
       </c>
       <c r="H9" s="52" t="n"/>
@@ -9764,12 +9764,12 @@
       </c>
       <c r="F10" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G10" s="47" t="inlineStr">
         <is>
-          <t>No WebRTC in SecureMarket.</t>
+          <t>SecureMarket is a JSON REST API; no WebRTC, TURN/STUN, DTLS-SRTP, or media/signaling servers are used.</t>
         </is>
       </c>
       <c r="H10" s="47" t="n"/>
@@ -9800,12 +9800,12 @@
       </c>
       <c r="F11" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G11" s="52" t="inlineStr">
         <is>
-          <t>No WebRTC or DTLS in SecureMarket.</t>
+          <t>SecureMarket is a JSON REST API; no WebRTC, TURN/STUN, DTLS-SRTP, or media/signaling servers are used.</t>
         </is>
       </c>
       <c r="H11" s="52" t="n"/>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="F12" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G12" s="47" t="inlineStr">
         <is>
-          <t>No WebRTC recording in SecureMarket.</t>
+          <t>SecureMarket is a JSON REST API; no WebRTC, TURN/STUN, DTLS-SRTP, or media/signaling servers are used.</t>
         </is>
       </c>
       <c r="H12" s="47" t="n"/>
@@ -9872,12 +9872,12 @@
       </c>
       <c r="F13" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G13" s="52" t="inlineStr">
         <is>
-          <t>No WebRTC or DTLS in SecureMarket.</t>
+          <t>SecureMarket is a JSON REST API; no WebRTC, TURN/STUN, DTLS-SRTP, or media/signaling servers are used.</t>
         </is>
       </c>
       <c r="H13" s="52" t="n"/>
@@ -9926,12 +9926,12 @@
       </c>
       <c r="F15" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G15" s="47" t="inlineStr">
         <is>
-          <t>No WebRTC signaling server in SecureMarket.</t>
+          <t>SecureMarket is a JSON REST API; no WebRTC, TURN/STUN, DTLS-SRTP, or media/signaling servers are used.</t>
         </is>
       </c>
       <c r="H15" s="47" t="n"/>
@@ -9962,12 +9962,12 @@
       </c>
       <c r="F16" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G16" s="52" t="inlineStr">
         <is>
-          <t>No WebRTC signaling server in SecureMarket.</t>
+          <t>SecureMarket is a JSON REST API; no WebRTC, TURN/STUN, DTLS-SRTP, or media/signaling servers are used.</t>
         </is>
       </c>
       <c r="H16" s="52" t="n"/>
@@ -10101,12 +10101,12 @@
       </c>
       <c r="F3" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G3" s="47" t="inlineStr">
         <is>
-          <t>Pydantic validates and decodes input once before processing.</t>
+          <t>Starlette/FastAPI decode the request once; Pydantic v2 schemas validate the parsed canonical values before any processing (schemas.py).</t>
         </is>
       </c>
       <c r="H3" s="47" t="n"/>
@@ -10137,12 +10137,12 @@
       </c>
       <c r="F4" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G4" s="52" t="inlineStr">
         <is>
-          <t>FastAPI/Pydantic performs output encoding as final step before response.</t>
+          <t>Output is JSON serialized by FastAPI as the final step; DB access is parameterized via SQLAlchemy ORM.</t>
         </is>
       </c>
       <c r="H4" s="52" t="n"/>
@@ -10191,12 +10191,12 @@
       </c>
       <c r="F6" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G6" s="47" t="inlineStr">
         <is>
-          <t>FastAPI returns JSON responses with correct Content-Type encoding.</t>
+          <t>API returns JSON only (application/json); FastAPI performs JSON output encoding. No server-side HTML/XML is generated.</t>
         </is>
       </c>
       <c r="H6" s="47" t="n"/>
@@ -10227,12 +10227,12 @@
       </c>
       <c r="F7" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G7" s="52" t="inlineStr">
         <is>
-          <t>FastAPI handles URL parameter encoding; no dynamic URL construction from user input.</t>
+          <t>Application does not build URLs from untrusted input; the only redirect is nginx HTTP-&gt;HTTPS to a fixed server_name.</t>
         </is>
       </c>
       <c r="H7" s="52" t="n"/>
@@ -10263,12 +10263,12 @@
       </c>
       <c r="F8" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G8" s="47" t="inlineStr">
         <is>
-          <t>SecureMarket is a REST API backend; no dynamic JavaScript content generated.</t>
+          <t>JSON responses are encoded by FastAPI/json; no dynamic JavaScript is generated (headless API).</t>
         </is>
       </c>
       <c r="H8" s="47" t="n"/>
@@ -10299,12 +10299,12 @@
       </c>
       <c r="F9" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G9" s="52" t="inlineStr">
         <is>
-          <t>SR-INPUT-07: SQLAlchemy ORM with parameterized queries only; raw SQL prohibited.</t>
+          <t>SQLAlchemy ORM used exclusively, no raw/string-built SQL (SR-INPUT-07). Verified by Semgrep p/sql-injection in CI.</t>
         </is>
       </c>
       <c r="H9" s="52" t="n"/>
@@ -10335,12 +10335,12 @@
       </c>
       <c r="F10" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G10" s="47" t="inlineStr">
         <is>
-          <t>No OS command execution from user input; filesystem operations use UUID-based paths.</t>
+          <t>No OS command execution (no os.system/subprocess/shell). Enforced by Bandit/Semgrep SAST gate.</t>
         </is>
       </c>
       <c r="H10" s="47" t="n"/>
@@ -10371,12 +10371,12 @@
       </c>
       <c r="F11" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G11" s="52" t="inlineStr">
         <is>
-          <t>No LDAP integration in SecureMarket.</t>
+          <t>No LDAP usage.</t>
         </is>
       </c>
       <c r="H11" s="52" t="n"/>
@@ -10407,12 +10407,12 @@
       </c>
       <c r="F12" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G12" s="47" t="inlineStr">
         <is>
-          <t>No XPath or XML processing in SecureMarket.</t>
+          <t>No XPath/XML query usage.</t>
         </is>
       </c>
       <c r="H12" s="47" t="n"/>
@@ -10443,12 +10443,12 @@
       </c>
       <c r="F13" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G13" s="52" t="inlineStr">
         <is>
-          <t>No LaTeX processing in SecureMarket.</t>
+          <t>No LaTeX processing.</t>
         </is>
       </c>
       <c r="H13" s="52" t="n"/>
@@ -10479,12 +10479,12 @@
       </c>
       <c r="F14" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G14" s="47" t="inlineStr">
         <is>
-          <t>Pydantic regex validators escape special characters correctly.</t>
+          <t>No regular expressions built from untrusted input.</t>
         </is>
       </c>
       <c r="H14" s="47" t="n"/>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="F15" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G15" s="52" t="inlineStr">
         <is>
-          <t>SR-INPUT-05: Export generation sanitizes metacharacters; template injection prevented.</t>
+          <t>No CSV/spreadsheet export feature; invoices are rendered as PDF (reportlab).</t>
         </is>
       </c>
       <c r="H15" s="52" t="n"/>
@@ -10569,12 +10569,12 @@
       </c>
       <c r="F17" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G17" s="47" t="inlineStr">
         <is>
-          <t>SR-INPUT-06: bleach library strips HTML tags from all user-supplied text fields.</t>
+          <t>No WYSIWYG/HTML input and no HTML rendering; user text (reviews, product fields) is stored and returned as JSON. SR-INPUT-06 (bleach) was designed but is unused; not exploitable without an HTML render context.</t>
         </is>
       </c>
       <c r="H17" s="47" t="n"/>
@@ -10605,12 +10605,12 @@
       </c>
       <c r="F18" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G18" s="52" t="inlineStr">
         <is>
-          <t>SAST-04: Bandit/Semgrep scan for eval(), exec(), and dynamic code execution. Prohibited by policy.</t>
+          <t>No eval()/exec()/dynamic code execution. Enforced by SAST (Bandit/Semgrep).</t>
         </is>
       </c>
       <c r="H18" s="52" t="n"/>
@@ -10641,12 +10641,12 @@
       </c>
       <c r="F19" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G19" s="47" t="inlineStr">
         <is>
-          <t>SR-INPUT-05, SR-INPUT-10: User data sanitized before use in Jinja2 templates and address fields.</t>
+          <t>Pydantic type validation plus some length bounds (review comment max 1000, password max 128); shipping address length/charset not bounded (SR-INPUT-10 not implemented).</t>
         </is>
       </c>
       <c r="H19" s="47" t="n"/>
@@ -10677,12 +10677,12 @@
       </c>
       <c r="F20" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G20" s="52" t="inlineStr">
         <is>
-          <t>No SVG uploads accepted; only image/png, image/jpeg, image/webp allowed (SR-INPUT-02).</t>
+          <t>SVG is not an accepted upload type (allow-list: png/jpeg/gif/webp with magic-byte checks).</t>
         </is>
       </c>
       <c r="H20" s="52" t="n"/>
@@ -10713,12 +10713,12 @@
       </c>
       <c r="F21" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G21" s="47" t="inlineStr">
         <is>
-          <t>SR-INPUT-05: Jinja2 SandboxedEnvironment with auto-escaping used for invoice/export generation.</t>
+          <t>No Markdown/CSS/XSL/BBCode processing of user content.</t>
         </is>
       </c>
       <c r="H21" s="47" t="n"/>
@@ -10749,12 +10749,12 @@
       </c>
       <c r="F22" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G22" s="52" t="inlineStr">
         <is>
-          <t>No external service calls initiated from user-supplied URLs. No SSRF surface.</t>
+          <t>Only outbound call is to a fixed HIBP endpoint (services/pwned.py); no user-supplied URLs are fetched, so SSRF surface is absent.</t>
         </is>
       </c>
       <c r="H22" s="52" t="n"/>
@@ -10785,12 +10785,12 @@
       </c>
       <c r="F23" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G23" s="47" t="inlineStr">
         <is>
-          <t>SR-INPUT-05: Jinja2 SandboxedEnvironment prevents template injection; user input escaped.</t>
+          <t>Invoices are produced with reportlab canvas drawString (no template engine); no template is built from untrusted input (SR-INPUT-05). Verified by SAST-06.</t>
         </is>
       </c>
       <c r="H23" s="47" t="n"/>
@@ -10821,12 +10821,12 @@
       </c>
       <c r="F24" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G24" s="52" t="inlineStr">
         <is>
-          <t>Python application; no JNDI usage.</t>
+          <t>Python stack; no JNDI.</t>
         </is>
       </c>
       <c r="H24" s="52" t="n"/>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="F25" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G25" s="47" t="inlineStr">
         <is>
-          <t>No memcache usage in SecureMarket.</t>
+          <t>No memcache.</t>
         </is>
       </c>
       <c r="H25" s="47" t="n"/>
@@ -10893,12 +10893,12 @@
       </c>
       <c r="F26" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G26" s="52" t="inlineStr">
         <is>
-          <t>SR-INPUT-05: Format strings in Jinja2 templates sanitized; bleach applied to user text fields.</t>
+          <t>Logging uses parameterized format args (logger.info("...%s", x)); no user-controlled format strings.</t>
         </is>
       </c>
       <c r="H26" s="52" t="n"/>
@@ -10929,12 +10929,12 @@
       </c>
       <c r="F27" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G27" s="47" t="inlineStr">
         <is>
-          <t>No mail system integration in SecureMarket.</t>
+          <t>No SMTP/IMAP integration (reset token surfaced in dev response; production email not implemented).</t>
         </is>
       </c>
       <c r="H27" s="47" t="n"/>
@@ -10965,12 +10965,12 @@
       </c>
       <c r="F28" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G28" s="52" t="inlineStr">
         <is>
-          <t>Pydantic uses safe regex patterns; SAST scanning checks for ReDoS-vulnerable patterns.</t>
+          <t>No custom regex applied to untrusted input; Pydantic EmailStr uses a safe validator.</t>
         </is>
       </c>
       <c r="H28" s="52" t="n"/>
@@ -11019,12 +11019,12 @@
       </c>
       <c r="F30" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G30" s="47" t="inlineStr">
         <is>
-          <t>Python is a memory-managed language; no manual memory management required.</t>
+          <t>Python is a memory-safe runtime; no manual buffer/pointer handling.</t>
         </is>
       </c>
       <c r="H30" s="47" t="n"/>
@@ -11055,12 +11055,12 @@
       </c>
       <c r="F31" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G31" s="52" t="inlineStr">
         <is>
-          <t>Pydantic enforces type constraints including numeric ranges (SR-INPUT-09).</t>
+          <t>Python integers are arbitrary precision; Pydantic enforces int typing.</t>
         </is>
       </c>
       <c r="H31" s="52" t="n"/>
@@ -11091,12 +11091,12 @@
       </c>
       <c r="F32" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G32" s="47" t="inlineStr">
         <is>
-          <t>Python garbage collection handles memory management automatically.</t>
+          <t>Managed runtime with garbage collection; no manual memory management.</t>
         </is>
       </c>
       <c r="H32" s="47" t="n"/>
@@ -11145,12 +11145,12 @@
       </c>
       <c r="F34" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G34" s="47" t="inlineStr">
         <is>
-          <t>No XML processing in SecureMarket; JSON-only API.</t>
+          <t>No XML parsing in the application.</t>
         </is>
       </c>
       <c r="H34" s="47" t="n"/>
@@ -11181,12 +11181,12 @@
       </c>
       <c r="F35" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G35" s="52" t="inlineStr">
         <is>
-          <t>Pydantic strict type validation; no pickle or unsafe deserialization used.</t>
+          <t>Only JSON is deserialized via Pydantic; no pickle/yaml.load of untrusted data.</t>
         </is>
       </c>
       <c r="H35" s="52" t="n"/>
@@ -11217,12 +11217,12 @@
       </c>
       <c r="F36" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G36" s="47" t="inlineStr">
         <is>
-          <t>FastAPI uses consistent JSON parsing via Pydantic; single parser for all JSON input.</t>
+          <t>A single canonical JSON parser (FastAPI/Pydantic) is used for request bodies.</t>
         </is>
       </c>
       <c r="H36" s="47" t="n"/>
@@ -11356,12 +11356,12 @@
       </c>
       <c r="F3" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G3" s="47" t="inlineStr">
         <is>
-          <t>SR-INPUT-01: Pydantic schemas document and enforce input validation rules for all endpoints.</t>
+          <t>Input validation rules are documented in the Phase 1 report (NFR-07, SR-INPUT) and implemented as Pydantic schemas (schemas.py).</t>
         </is>
       </c>
       <c r="H3" s="47" t="n"/>
@@ -11392,12 +11392,12 @@
       </c>
       <c r="F4" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G4" s="52" t="inlineStr">
         <is>
-          <t>SR-INPUT-09, SR-INPUT-10: Combined field validation documented (price, stock, address formats).</t>
+          <t>Some combined-data checks exist (e.g. all order items must share one seller); contextual consistency is not comprehensively documented.</t>
         </is>
       </c>
       <c r="H4" s="52" t="n"/>
@@ -11428,12 +11428,12 @@
       </c>
       <c r="F5" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G5" s="47" t="inlineStr">
         <is>
-          <t>SR-BIZ-01 to SR-BIZ-07: Business logic limits documented (max images, review eligibility, order state machine).</t>
+          <t>Some business limits documented/implemented (max 10 images/product, 200MB/seller quota, lockout); not a complete documented set.</t>
         </is>
       </c>
       <c r="H5" s="47" t="n"/>
@@ -11482,12 +11482,12 @@
       </c>
       <c r="F7" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G7" s="47" t="inlineStr">
         <is>
-          <t>SR-INPUT-01: All inputs validated server-side via Pydantic with strict type checking; returns 422 on failure.</t>
+          <t>Positive validation via Pydantic + field validators (price&gt;0, stock&gt;=0, rating 1-5, quantity&gt;0).</t>
         </is>
       </c>
       <c r="H7" s="47" t="n"/>
@@ -11518,12 +11518,12 @@
       </c>
       <c r="F8" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G8" s="52" t="inlineStr">
         <is>
-          <t>All validation enforced at the API/Application layer; no client-side security controls relied upon.</t>
+          <t>All validation runs server-side (Pydantic at the API layer plus service-layer checks).</t>
         </is>
       </c>
       <c r="H8" s="52" t="n"/>
@@ -11554,12 +11554,12 @@
       </c>
       <c r="F9" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G9" s="47" t="inlineStr">
         <is>
-          <t>Pydantic model validators enforce logical consistency of combined fields.</t>
+          <t>Related-item consistency enforced (same-seller order, stock availability) before persistence.</t>
         </is>
       </c>
       <c r="H9" s="47" t="n"/>
@@ -11608,12 +11608,12 @@
       </c>
       <c r="F11" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G11" s="47" t="inlineStr">
         <is>
-          <t>SR-BIZ-03: Order status transitions follow defined state machine; steps cannot be skipped.</t>
+          <t>Order lifecycle enforced by a state machine (_is_valid_status_transition in routers/orders.py).</t>
         </is>
       </c>
       <c r="H11" s="47" t="n"/>
@@ -11644,12 +11644,12 @@
       </c>
       <c r="F12" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G12" s="52" t="inlineStr">
         <is>
-          <t>SR-BIZ-01 to SR-BIZ-07: All documented business logic limits implemented and enforced.</t>
+          <t>Business limits enforced: stock checks, image quota/count, review-requires-delivered-purchase.</t>
         </is>
       </c>
       <c r="H12" s="52" t="n"/>
@@ -11680,12 +11680,12 @@
       </c>
       <c r="F13" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G13" s="47" t="inlineStr">
         <is>
-          <t>SQLAlchemy transactions ensure atomicity; operations roll back on failure.</t>
+          <t>Each use case runs in a single SQLAlchemy transaction (commit/rollback), e.g. order creation.</t>
         </is>
       </c>
       <c r="H13" s="47" t="n"/>
@@ -11716,12 +11716,12 @@
       </c>
       <c r="F14" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G14" s="52" t="inlineStr">
         <is>
-          <t>SR-DATA-10: Database-level SELECT FOR UPDATE locking prevents double-booking of stock.</t>
+          <t>Stock is decremented inside a transaction but without SELECT ... FOR UPDATE row locking (SR-DATA-10 designed, not implemented); concurrent orders can race. Acknowledged in test_business.py.</t>
         </is>
       </c>
       <c r="H14" s="52" t="n"/>
@@ -11752,12 +11752,12 @@
       </c>
       <c r="F15" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G15" s="47" t="inlineStr">
         <is>
-          <t>Not applicable for marketplace operations at this scale; no high-value approval workflows defined.</t>
+          <t>No high-value flow requires multi-user approval in scope (admin actions are single-actor).</t>
         </is>
       </c>
       <c r="H15" s="47" t="n"/>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="F17" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G17" s="47" t="inlineStr">
         <is>
-          <t>SR-AUTH-09: Rate limiting on login (5/min per IP). NFR-04: 100 req/min for other endpoints.</t>
+          <t>Account lockout (5 attempts / 30 min) is implemented; general per-IP/per-endpoint rate limiting (SR-AUTH-09, NFR-04) is documented but the middleware is not implemented (test skipped).</t>
         </is>
       </c>
       <c r="H17" s="47" t="n"/>
@@ -11842,12 +11842,12 @@
       </c>
       <c r="F18" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="G18" s="52" t="inlineStr">
         <is>
-          <t>Human timing requirements not implemented; rate limiting used instead.</t>
+          <t>No human-timing/anti-automation pacing controls implemented.</t>
         </is>
       </c>
       <c r="H18" s="52" t="n"/>
@@ -11981,12 +11981,12 @@
       </c>
       <c r="F3" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G3" s="47" t="inlineStr">
         <is>
-          <t>SecureMarket is a REST API backend with no browser client.</t>
+          <t>Headless JSON API; no browser client is shipped. Proxy security headers (HSTS/CSP) are documented in the report.</t>
         </is>
       </c>
       <c r="H3" s="47" t="n"/>
@@ -12035,12 +12035,12 @@
       </c>
       <c r="F5" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G5" s="47" t="inlineStr">
         <is>
-          <t>SR-DATA-03: Files served with Content-Disposition: attachment preventing unintended rendering.</t>
+          <t>nginx sets X-Content-Type-Options: nosniff and CSP default-src 'none'; invoice downloads use Content-Disposition: attachment (routers/orders.py).</t>
         </is>
       </c>
       <c r="H5" s="47" t="n"/>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="F6" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G6" s="52" t="inlineStr">
         <is>
-          <t>No frontend application; REST API only.</t>
+          <t>No client-side rendering (no HTML/DOM output).</t>
         </is>
       </c>
       <c r="H6" s="52" t="n"/>
@@ -12107,12 +12107,12 @@
       </c>
       <c r="F7" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G7" s="47" t="inlineStr">
         <is>
-          <t>No JavaScript frontend application.</t>
+          <t>No client-side JavaScript.</t>
         </is>
       </c>
       <c r="H7" s="47" t="n"/>
@@ -12161,12 +12161,12 @@
       </c>
       <c r="F9" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G9" s="47" t="inlineStr">
         <is>
-          <t>SecureMarket uses JWT in Authorization header, not cookies.</t>
+          <t>No cookies used; auth is a bearer JWT in the Authorization header.</t>
         </is>
       </c>
       <c r="H9" s="47" t="n"/>
@@ -12197,12 +12197,12 @@
       </c>
       <c r="F10" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G10" s="52" t="inlineStr">
         <is>
-          <t>No cookies used; JWT tokens only.</t>
+          <t>No cookies used.</t>
         </is>
       </c>
       <c r="H10" s="52" t="n"/>
@@ -12233,12 +12233,12 @@
       </c>
       <c r="F11" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G11" s="47" t="inlineStr">
         <is>
-          <t>No cookies used; JWT tokens only.</t>
+          <t>No cookies used.</t>
         </is>
       </c>
       <c r="H11" s="47" t="n"/>
@@ -12269,12 +12269,12 @@
       </c>
       <c r="F12" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G12" s="52" t="inlineStr">
         <is>
-          <t>No cookies used; JWT tokens only.</t>
+          <t>No cookies used; tokens are returned in the JSON body, not Set-Cookie.</t>
         </is>
       </c>
       <c r="H12" s="52" t="n"/>
@@ -12305,12 +12305,12 @@
       </c>
       <c r="F13" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G13" s="47" t="inlineStr">
         <is>
-          <t>No cookies used; JWT tokens only.</t>
+          <t>No cookies used.</t>
         </is>
       </c>
       <c r="H13" s="47" t="n"/>
@@ -12359,12 +12359,12 @@
       </c>
       <c r="F15" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G15" s="47" t="inlineStr">
         <is>
-          <t>SR-COMM-02: HSTS header set with max-age=31536000; includeSubDomains.</t>
+          <t>nginx sets Strict-Transport-Security max-age=63072000; includeSubDomains; preload on all responses (SR-COMM-02).</t>
         </is>
       </c>
       <c r="H15" s="47" t="n"/>
@@ -12395,12 +12395,12 @@
       </c>
       <c r="F16" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G16" s="52" t="inlineStr">
         <is>
-          <t>SR-COMM-04: CORS restricted to explicit allowlist; no wildcard origins.</t>
+          <t>CORS uses an explicit origin allow-list from settings; no wildcard with credentials (main.py, SR-COMM-04).</t>
         </is>
       </c>
       <c r="H16" s="52" t="n"/>
@@ -12431,12 +12431,12 @@
       </c>
       <c r="F17" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G17" s="47" t="inlineStr">
         <is>
-          <t>SR-COMM-05: Content-Security-Policy: default-src 'none' set on authenticated responses.</t>
+          <t>nginx sets CSP default-src 'none'; frame-ancestors 'none' (covers object-src); base-uri 'none' is not explicitly set.</t>
         </is>
       </c>
       <c r="H17" s="47" t="n"/>
@@ -12467,12 +12467,12 @@
       </c>
       <c r="F18" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G18" s="52" t="inlineStr">
         <is>
-          <t>SR-COMM-05: X-Content-Type-Options: nosniff set on all responses.</t>
+          <t>nginx sets X-Content-Type-Options: nosniff on all responses.</t>
         </is>
       </c>
       <c r="H18" s="52" t="n"/>
@@ -12503,12 +12503,12 @@
       </c>
       <c r="F19" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G19" s="47" t="inlineStr">
         <is>
-          <t>Referrer-Policy header included in security middleware stack.</t>
+          <t>nginx sets Referrer-Policy: no-referrer.</t>
         </is>
       </c>
       <c r="H19" s="47" t="n"/>
@@ -12539,12 +12539,12 @@
       </c>
       <c r="F20" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G20" s="52" t="inlineStr">
         <is>
-          <t>SR-COMM-05: X-Frame-Options: DENY set (frame-ancestors equivalent).</t>
+          <t>nginx CSP includes frame-ancestors 'none' on every response (X-Frame-Options: DENY also set).</t>
         </is>
       </c>
       <c r="H20" s="52" t="n"/>
@@ -12575,12 +12575,12 @@
       </c>
       <c r="F21" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="G21" s="47" t="inlineStr">
         <is>
-          <t>CSP violation reporting endpoint not implemented in Phase 1.</t>
+          <t>No CSP violation reporting endpoint configured.</t>
         </is>
       </c>
       <c r="H21" s="47" t="n"/>
@@ -12611,12 +12611,12 @@
       </c>
       <c r="F22" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G22" s="52" t="inlineStr">
         <is>
-          <t>REST API; no HTML document rendering initiated.</t>
+          <t>Responses are JSON, not document (text/html) renders; COOP not applicable.</t>
         </is>
       </c>
       <c r="H22" s="52" t="n"/>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="F24" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G24" s="47" t="inlineStr">
         <is>
-          <t>JWT in Authorization header (not cookies); CORS preflight enforces origin validation (SR-COMM-04).</t>
+          <t>Auth uses a stateless bearer token (no cookies/ambient credentials), so the API is not exposed to CSRF.</t>
         </is>
       </c>
       <c r="H24" s="47" t="n"/>
@@ -12701,12 +12701,12 @@
       </c>
       <c r="F25" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G25" s="52" t="inlineStr">
         <is>
-          <t>SR-COMM-04: CORS allowlist validation; preflight required for cross-origin requests.</t>
+          <t>The custom Authorization header forces a CORS preflight; no cookie-based ambient auth to bypass.</t>
         </is>
       </c>
       <c r="H25" s="52" t="n"/>
@@ -12737,12 +12737,12 @@
       </c>
       <c r="F26" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G26" s="47" t="inlineStr">
         <is>
-          <t>REST API uses appropriate HTTP methods (POST, PUT, PATCH, DELETE) for state-changing operations.</t>
+          <t>State-changing operations use POST/PATCH/PUT/DELETE; GET is read-only.</t>
         </is>
       </c>
       <c r="H26" s="47" t="n"/>
@@ -12773,12 +12773,12 @@
       </c>
       <c r="F27" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G27" s="52" t="inlineStr">
         <is>
-          <t>Single API application; no cross-origin application separation required.</t>
+          <t>Single application; no multi-app same-origin separation needed.</t>
         </is>
       </c>
       <c r="H27" s="52" t="n"/>
@@ -12809,12 +12809,12 @@
       </c>
       <c r="F28" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G28" s="47" t="inlineStr">
         <is>
-          <t>No postMessage usage; REST API backend only.</t>
+          <t>No postMessage usage (no client JS).</t>
         </is>
       </c>
       <c r="H28" s="47" t="n"/>
@@ -12845,12 +12845,12 @@
       </c>
       <c r="F29" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G29" s="52" t="inlineStr">
         <is>
-          <t>No JSONP; REST API returns JSON with Content-Type: application/json.</t>
+          <t>No JSONP.</t>
         </is>
       </c>
       <c r="H29" s="52" t="n"/>
@@ -12881,12 +12881,12 @@
       </c>
       <c r="F30" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G30" s="47" t="inlineStr">
         <is>
-          <t>No script resources containing authorized data.</t>
+          <t>No JavaScript resources are served.</t>
         </is>
       </c>
       <c r="H30" s="47" t="n"/>
@@ -12917,12 +12917,12 @@
       </c>
       <c r="F31" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G31" s="52" t="inlineStr">
         <is>
-          <t>SR-DATA-03: Files served through authenticated API endpoints only; not directly accessible.</t>
+          <t>Product images are intentionally public; the authenticated resource (invoices) is served via API with auth. No cross-origin embedding scenario for a JSON API.</t>
         </is>
       </c>
       <c r="H31" s="52" t="n"/>
@@ -12971,12 +12971,12 @@
       </c>
       <c r="F33" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G33" s="47" t="inlineStr">
         <is>
-          <t>No external CDN assets; self-contained REST API.</t>
+          <t>No externally hosted client-side assets/CDN.</t>
         </is>
       </c>
       <c r="H33" s="47" t="n"/>
@@ -13025,12 +13025,12 @@
       </c>
       <c r="F35" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G35" s="47" t="inlineStr">
         <is>
-          <t>REST API backend; no client-side technology stack.</t>
+          <t>No client-side technologies in use.</t>
         </is>
       </c>
       <c r="H35" s="47" t="n"/>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="F36" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G36" s="52" t="inlineStr">
         <is>
-          <t>No automatic redirects to external domains.</t>
+          <t>No user-controlled redirects; nginx redirects only to its fixed server_name (avoids Host-header open redirect).</t>
         </is>
       </c>
       <c r="H36" s="52" t="n"/>
@@ -13097,12 +13097,12 @@
       </c>
       <c r="F37" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G37" s="47" t="inlineStr">
         <is>
-          <t>No external redirects implemented.</t>
+          <t>No redirects to external/uncontrolled destinations.</t>
         </is>
       </c>
       <c r="H37" s="47" t="n"/>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="F38" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G38" s="52" t="inlineStr">
         <is>
-          <t>Phase 1 design; HSTS preload list registration not applicable.</t>
+          <t>HSTS header includes the 'preload' directive, but the production domain is a placeholder and not yet submitted to the browser preload list.</t>
         </is>
       </c>
       <c r="H38" s="52" t="n"/>
@@ -13169,12 +13169,12 @@
       </c>
       <c r="F39" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G39" s="47" t="inlineStr">
         <is>
-          <t>REST API; no browser security feature dependency.</t>
+          <t>No browser client to degrade.</t>
         </is>
       </c>
       <c r="H39" s="47" t="n"/>
@@ -13308,12 +13308,12 @@
       </c>
       <c r="F3" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G3" s="47" t="inlineStr">
         <is>
-          <t>FastAPI automatically sets Content-Type: application/json with UTF-8 charset on all responses.</t>
+          <t>FastAPI responses carry Content-Type: application/json with UTF-8 encoding.</t>
         </is>
       </c>
       <c r="H3" s="47" t="n"/>
@@ -13344,12 +13344,12 @@
       </c>
       <c r="F4" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G4" s="52" t="inlineStr">
         <is>
-          <t>SR-COMM-01: HTTP redirects to HTTPS via Nginx reverse proxy (301 redirect).</t>
+          <t>nginx redirects all HTTP to HTTPS (301). For a pure API, non-browser endpoints should ideally reject rather than transparently redirect to surface accidental plaintext use.</t>
         </is>
       </c>
       <c r="H4" s="52" t="n"/>
@@ -13380,12 +13380,12 @@
       </c>
       <c r="F5" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G5" s="47" t="inlineStr">
         <is>
-          <t>Nginx configured as reverse proxy; X-Real-IP and X-Forwarded-* headers managed at proxy level.</t>
+          <t>nginx overwrites X-Real-IP/X-Forwarded-For from the real connection and the app is reachable only via the proxy (not published). (uvicorn --forwarded-allow-ips is broad but the app is network-isolated.)</t>
         </is>
       </c>
       <c r="H5" s="47" t="n"/>
@@ -13416,12 +13416,12 @@
       </c>
       <c r="F6" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G6" s="52" t="inlineStr">
         <is>
-          <t>FastAPI route decorators define explicit HTTP methods; unsupported methods return 405.</t>
+          <t>Only declared route methods are served; FastAPI returns 405 for unsupported methods; CORS lists allowed methods.</t>
         </is>
       </c>
       <c r="H6" s="52" t="n"/>
@@ -13452,12 +13452,12 @@
       </c>
       <c r="F7" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G7" s="47" t="inlineStr">
         <is>
-          <t>Per-message digital signatures not required for SecureMarket transactions.</t>
+          <t>No per-message digital signature requirement for in-scope transactions.</t>
         </is>
       </c>
       <c r="H7" s="47" t="n"/>
@@ -13506,12 +13506,12 @@
       </c>
       <c r="F9" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G9" s="47" t="inlineStr">
         <is>
-          <t>Nginx and FastAPI handle HTTP message boundary determination correctly per HTTP spec.</t>
+          <t>Message framing handled by nginx (HTTP/2 enabled) and uvicorn; no custom HTTP parsing.</t>
         </is>
       </c>
       <c r="H9" s="47" t="n"/>
@@ -13542,12 +13542,12 @@
       </c>
       <c r="F10" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G10" s="52" t="inlineStr">
         <is>
-          <t>FastAPI generates consistent Content-Length headers matching response body length.</t>
+          <t>Content-Length/framing handled by nginx and uvicorn.</t>
         </is>
       </c>
       <c r="H10" s="52" t="n"/>
@@ -13578,12 +13578,12 @@
       </c>
       <c r="F11" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G11" s="47" t="inlineStr">
         <is>
-          <t>Nginx handles HTTP/2 connection-specific header filtering.</t>
+          <t>Connection-specific headers handled/normalized by nginx and uvicorn.</t>
         </is>
       </c>
       <c r="H11" s="47" t="n"/>
@@ -13614,12 +13614,12 @@
       </c>
       <c r="F12" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G12" s="52" t="inlineStr">
         <is>
-          <t>Nginx rejects HTTP/2 headers containing CR/LF sequences.</t>
+          <t>CR/LF in header fields rejected by nginx/uvicorn HTTP parsing.</t>
         </is>
       </c>
       <c r="H12" s="52" t="n"/>
@@ -13650,12 +13650,12 @@
       </c>
       <c r="F13" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G13" s="47" t="inlineStr">
         <is>
-          <t>Nginx configures client_max_body_size and header size limits to prevent DoS.</t>
+          <t>nginx enforces default URI/header size limits and client_max_body_size 10m.</t>
         </is>
       </c>
       <c r="H13" s="47" t="n"/>
@@ -13704,12 +13704,12 @@
       </c>
       <c r="F15" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G15" s="47" t="inlineStr">
         <is>
-          <t>No GraphQL; REST API only.</t>
+          <t>No GraphQL endpoint.</t>
         </is>
       </c>
       <c r="H15" s="47" t="n"/>
@@ -13740,12 +13740,12 @@
       </c>
       <c r="F16" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G16" s="52" t="inlineStr">
         <is>
-          <t>No GraphQL; REST API only.</t>
+          <t>No GraphQL endpoint.</t>
         </is>
       </c>
       <c r="H16" s="52" t="n"/>
@@ -13794,12 +13794,12 @@
       </c>
       <c r="F18" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G18" s="47" t="inlineStr">
         <is>
-          <t>No WebSocket connections in SecureMarket.</t>
+          <t>No WebSocket endpoints.</t>
         </is>
       </c>
       <c r="H18" s="47" t="n"/>
@@ -13830,12 +13830,12 @@
       </c>
       <c r="F19" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G19" s="52" t="inlineStr">
         <is>
-          <t>No WebSocket connections in SecureMarket.</t>
+          <t>No WebSocket endpoints.</t>
         </is>
       </c>
       <c r="H19" s="52" t="n"/>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="F20" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G20" s="47" t="inlineStr">
         <is>
-          <t>No WebSocket connections in SecureMarket.</t>
+          <t>No WebSocket endpoints.</t>
         </is>
       </c>
       <c r="H20" s="47" t="n"/>
@@ -13902,12 +13902,12 @@
       </c>
       <c r="F21" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G21" s="52" t="inlineStr">
         <is>
-          <t>No WebSocket connections in SecureMarket.</t>
+          <t>No WebSocket endpoints.</t>
         </is>
       </c>
       <c r="H21" s="52" t="n"/>
@@ -14041,12 +14041,12 @@
       </c>
       <c r="F3" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G3" s="47" t="inlineStr">
         <is>
-          <t>SR-INPUT-02, SR-INPUT-03: Permitted file types (png/jpeg/webp), max 10MB, and handling behavior documented.</t>
+          <t>Permitted types, extensions and 10MB size limit documented (NFR-06, SR-INPUT-02/03) and enforced (core/image_service.py); rejected files return 4xx.</t>
         </is>
       </c>
       <c r="H3" s="47" t="n"/>
@@ -14095,12 +14095,12 @@
       </c>
       <c r="F5" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G5" s="47" t="inlineStr">
         <is>
-          <t>SR-INPUT-03: 10MB maximum file size enforced at both API and filesystem layers.</t>
+          <t>10MB upload limit enforced at the API (routers/images.py) and at nginx (client_max_body_size 10m).</t>
         </is>
       </c>
       <c r="H5" s="47" t="n"/>
@@ -14131,12 +14131,12 @@
       </c>
       <c r="F6" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G6" s="52" t="inlineStr">
         <is>
-          <t>SR-INPUT-02: File extension AND magic bytes validated before acceptance.</t>
+          <t>Extension + declared MIME + magic-byte detection with cross-check (image_service.validate_*), SR-INPUT-02.</t>
         </is>
       </c>
       <c r="H6" s="52" t="n"/>
@@ -14167,12 +14167,12 @@
       </c>
       <c r="F7" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G7" s="47" t="inlineStr">
         <is>
-          <t>No compressed file uploads accepted; images only.</t>
+          <t>No archive/compressed-file uploads are accepted (images only).</t>
         </is>
       </c>
       <c r="H7" s="47" t="n"/>
@@ -14203,12 +14203,12 @@
       </c>
       <c r="F8" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G8" s="52" t="inlineStr">
         <is>
-          <t>SR-DATA-09: 200MB per-seller quota enforced. SR-BIZ-07: Maximum 10 images per product.</t>
+          <t>Per-seller 200MB quota and max 10 images per product enforced (services/image_use_case.py).</t>
         </is>
       </c>
       <c r="H8" s="52" t="n"/>
@@ -14239,12 +14239,12 @@
       </c>
       <c r="F9" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G9" s="47" t="inlineStr">
         <is>
-          <t>No compressed file uploads; symlink risk not applicable.</t>
+          <t>No compressed uploads; save_file also rejects symlink targets.</t>
         </is>
       </c>
       <c r="H9" s="47" t="n"/>
@@ -14275,12 +14275,12 @@
       </c>
       <c r="F10" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="G10" s="52" t="inlineStr">
         <is>
-          <t>No pixel size limit defined; 10MB file size limit provides partial mitigation.</t>
+          <t>Byte size is limited (10MB) but image pixel dimensions are not validated (no pixel-flood check).</t>
         </is>
       </c>
       <c r="H10" s="52" t="n"/>
@@ -14329,12 +14329,12 @@
       </c>
       <c r="F12" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G12" s="47" t="inlineStr">
         <is>
-          <t>SR-DATA-03: Files stored outside web root; not directly executable via HTTP request.</t>
+          <t>Uploads are stored in a non-web-root uploads dir and served via FileResponse with fixed media types; nginx does not execute them.</t>
         </is>
       </c>
       <c r="H12" s="47" t="n"/>
@@ -14365,12 +14365,12 @@
       </c>
       <c r="F13" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G13" s="52" t="inlineStr">
         <is>
-          <t>SR-DATA-01, SR-INPUT-04: UUID filenames generated server-side; user-supplied filenames never used in path construction.</t>
+          <t>Server-generated UUID filenames; path-traversal/null-byte/symlink rejection; original filename sanitized (SR-INPUT-04, SR-DATA-01).</t>
         </is>
       </c>
       <c r="H13" s="52" t="n"/>
@@ -14401,12 +14401,12 @@
       </c>
       <c r="F14" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="G14" s="47" t="inlineStr">
         <is>
-          <t>No compressed file processing; zip slip not applicable.</t>
+          <t>No server-side decompression (no zip-slip surface).</t>
         </is>
       </c>
       <c r="H14" s="47" t="n"/>
@@ -14455,12 +14455,12 @@
       </c>
       <c r="F16" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G16" s="47" t="inlineStr">
         <is>
-          <t>SR-DATA-03: Content-Disposition: attachment header set on all file downloads.</t>
+          <t>Served names are server-generated UUIDs; image paths are validated (build_safe_path); invoice downloads set Content-Disposition with a filename.</t>
         </is>
       </c>
       <c r="H16" s="47" t="n"/>
@@ -14491,12 +14491,12 @@
       </c>
       <c r="F17" s="49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Compliant</t>
         </is>
       </c>
       <c r="G17" s="52" t="inlineStr">
         <is>
-          <t>SR-DATA-01: UUID filenames used in responses; original filenames stored in DB only, never in HTTP headers.</t>
+          <t>Served filenames are UUID-based and safe; no untrusted filename is reflected in headers.</t>
         </is>
       </c>
       <c r="H17" s="52" t="n"/>
@@ -14527,12 +14527,12 @@
       </c>
       <c r="F18" s="49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="G18" s="47" t="inlineStr">
         <is>
-          <t>Antivirus scanning not implemented; magic byte validation and MIME type checking used as primary controls.</t>
+          <t>Magic-byte validation is performed, but uploads are not scanned by antivirus.</t>
         </is>
       </c>
       <c r="H18" s="47" t="n"/>
